--- a/matriz trazabilidad/Matriz_Trazabilidad_Overfore_Informe1_v1.1.xlsx
+++ b/matriz trazabilidad/Matriz_Trazabilidad_Overfore_Informe1_v1.1.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Informe 1. Contiene los 228 requerimientos del catálogo v2.4 con su origen, su componente de arquitectura, su prueba de verificación y el criterio de aceptación que sostiene. La columna de paquete de la EDT se completa en el Informe 2, instancia en que el Formulario T-22 exige la estructura de descomposición del trabajo.</t>
+          <t>Informe 1. Contiene los 228 requerimientos del catálogo v2.4 con su origen, su componente de arquitectura, su prueba de verificación y el criterio de aceptación que sostiene. La columna de paquete de la EDT se completa en el Informe 2, instancia en que el Formulario T-22 exige la estructura de descomposición del trabajo. Revisión de consistencia del 1 de septiembre de 2026: se alinean etapa, prioridad y origen con el catálogo v2.4.1, se corrigen los componentes de RF-CAR-005 y RF-CAR-008 y el criterio de RF-CAR-005, y se recalculan las hojas «Componentes» y «Cobertura de criterios».</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Obligatorio, opcional de Etapa 1 u opcional de Etapa 2, según el catálogo.</t>
+          <t>Obligatorio, opcional de Etapa 1, opcional de Etapa 2, opcional diferido o excluido del Contrato, según el catálogo. Los excluidos conservan su especificación para que el CLIENTE pueda solicitarlos como cambio conforme al Artículo 72.º de las Bases Administrativas; no se comprometen ni se costean en esta oferta.</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Asignación conforme al apartado 2 del Subdocumento 3.</t>
+          <t>Asignación conforme al apartado 2 del Subdocumento 3 v1.4. «Fuera de alcance (Art. 72.º)» identifica los tres requerimientos que el apartado 3 excluye del Contrato en ambas etapas: prorrateo del viaje de borde (RF-CAR-008), factor de corrección de pesaje (RF-PES-006) y biometría de portería (RF-IDE-013).</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>C-20 — Administración, parametrización y auditoría</t>
+          <t>C-01 — Núcleo de trazabilidad del mineral (polígono, viaje, stock, lote)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>n.º 9</t>
+          <t>n.º 1</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Opcional - Etapa 2</t>
+          <t>Excluido del Contrato — incorporable como cambio (Art. 72.º BB.AA.)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Decisión 11 (prorrateo diferido a Etapa 2)</t>
+          <t>Decisión 11 (prorrateo excluido del Contrato en ambas etapas)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Etapa 1</t>
+          <t>Fuera de alcance (Art. 72.º)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>C-22 — Plataforma base: infraestructura, seguridad, identidad técnica y observabilidad</t>
+          <t>C-01 — Núcleo de trazabilidad del mineral (polígono, viaje, stock, lote)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Etapa 1</t>
+          <t>Etapa 2</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Excluido del Contrato — incorporable como cambio (Art. 72.º BB.AA.)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Decisión 2 (factor diferido a Etapa 2)</t>
+          <t>Decisión 2 (factor de corrección excluido del Contrato en ambas etapas)</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Etapa 1</t>
+          <t>Fuera de alcance (Art. 72.º)</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Etapa 1</t>
+          <t>Etapa 2</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Etapa 1</t>
+          <t>Etapa 2</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Opcional - diferido</t>
+          <t>Excluido del Contrato — incorporable como cambio (Art. 72.º BB.AA.)</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Decisión 13 (biometría diferida)</t>
+          <t>Decisión 13 (biometría de portería excluida del Contrato en ambas etapas)</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Etapa 1</t>
+          <t>Fuera de alcance (Art. 72.º)</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Decisión 13, advertencia de consistencia (no confundir el control de portería con el del recinto de servidores); Bases Técnicas Transversales, código del requisito de biometría facial por verificar</t>
+          <t>Decisión 13, advertencia de consistencia (no confundir el control de portería con el del recinto de servidores); Bases Técnicas Transversales, RT-06.20 (acceso biométrico facial con AFIS de respaldo)</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cap. 15, RT-17.06; Cap. 5</t>
+          <t>Cap. 15, RT-17.06 (plataforma de control de fatiga); Cap. 5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Subdocumento 3, apartado 5</t>
+          <t>Subdocumento 3, apartado 5 (método de verificación comprometido)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Subdocumento 3, apartado 2.4</t>
+          <t>Subdocumento 3, apartado 2.4 (compromiso de serie reconstruida)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cap. 18, criterio n.12</t>
+          <t>Cap. 18, criterio n.12 (auditable por un tercero)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cap. 15, RT-17.06</t>
+          <t>Cap. 15, RT-17.06 (periféricos a integrar)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Decisión 4; Bases Técnicas Transversales, RT-08.14 (código por verificar contra FEP02.26)</t>
+          <t>Decisión 4; Bases Técnicas Transversales, RT-08.14 (gestión centralizada de flota de dispositivos)</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Subdocumento 3, ap. 2.4 (bloque de migración de la Etapa 2)</t>
+          <t>Subdoc. 3 ap. 2.4 (bloque de migración de la Etapa 2)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Cap. 15, RT-09.02; Anexo B (peak de carga en el cambio de turno, 45 a 60 minutos); Bases Técnicas Transversales RT-09.06 y RT-09.07 (por verificar)</t>
+          <t>Cap. 15, RT-09.02; Anexo B (peak de carga en el cambio de turno, 45 a 60 minutos); Bases Técnicas Transversales RT-09.06 y RT-09.07</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Cap. 14.1 y Cap. 13.2 (crecimiento y replicación a una nueva unidad); Bases Técnicas Transversales RT-09.03, RT-09.04 y RT-08.05 (por verificar)</t>
+          <t>Cap. 14.1 y Cap. 13.2 (crecimiento y replicación a una nueva unidad); Bases Técnicas Transversales RT-09.03, RT-09.04 y RT-08.05</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Cap. 6 (3 a 6 cortes de fibra al año, de 4 a 20 horas); Restricción n.1; Bases Técnicas Transversales RT-10.01 y Bases Administrativas Art. 78 (por verificar)</t>
+          <t>Cap. 6 (3 a 6 cortes de fibra al año, de 4 a 20 horas); Restricción n.1; Bases Técnicas Transversales RT-10.01 (99,9 % mensual en servicios críticos); Bases Administrativas Art. 78</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>Cap. 18, criterio n.13; Decisión 9; Bases Técnicas Transversales RT-07.04 (por verificar)</t>
+          <t>Cap. 18, criterio n.13; Decisión 9; Bases Técnicas Transversales RT-07.04 (RTO 4 h, RPO 15 min)</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Cap. 6, recuadro; Cap. 17.4, punto 1; Bases Administrativas Art. 16 (por verificar)</t>
+          <t>Cap. 6, recuadro; Cap. 17.4, punto 1; Bases Administrativas Art. 16 (pendiente de contrastar contra la versión vigente de las Bases Administrativas)</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>Cap. 15, RT-16.30; Subdocumento 3, ap. 2.3 y 2.4</t>
+          <t>Cap. 15, RT-16.30 (portales autenticados de contratistas y compradores); Subdocumento 3, ap. 2.3 y 2.4</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Cap. 12 (IEC 62443 y segregación TI/TO); Restricción n.3; Bases Técnicas Transversales RT-11.20 (por verificar)</t>
+          <t>Cap. 12; Restricción n.3; Bases Técnicas Transversales RT-11.20 (pruebas de intrusión anuales por tercero independiente)</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>Cap. 16.1 n.10; Cap. 17.4, punto 5; Bases Técnicas Transversales, glosario de capa anticorrupción (por verificar)</t>
+          <t>Cap. 16.1 n.10; Cap. 17.4, punto 5; Bases Técnicas Transversales, RT-05.20 (capa anticorrupción)</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>Restricción n.10 (equipo de TI de once personas); Cap. 15, RT-05.10; Bases Técnicas Transversales, capítulo de observabilidad (por verificar)</t>
+          <t>Restricción n.10 (equipo de TI de once personas); Cap. 15, RT-05.10; Bases Técnicas Transversales RT-14.01 (observabilidad unificada con métricas, registros y trazas correlacionadas)</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>Cap. 17.6, punto 7 (transferencia de la operación al equipo del CLIENTE); Cap. 17.1; Bases Administrativas Art. 77 (por verificar)</t>
+          <t>Cap. 17.6, punto 7 (transferencia de la operación al equipo del CLIENTE); Cap. 17.1; Bases Administrativas Art. 77 (pendiente de contrastar contra la versión vigente de las Bases Administrativas)</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>Cap. 17.4, punto 1 (qué se ejecuta en faena y qué en la nube, componente por componente); Cap. 6, recuadro; Restricción n.2; Cap. 8, Alcaíno; Bases Administrativas Art. 16 (por verificar)</t>
+          <t>Cap. 17.4, punto 1; Cap. 6, recuadro; Restricción n.2; Cap. 8, Alcaíno; Bases Administrativas Art. 16 (pendiente de contrastar contra la versión vigente de las Bases Administrativas)</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>Restricción n.12 (Reglamento de Seguridad Minera); Bases Técnicas Transversales, capítulo 15 (por verificar)</t>
+          <t>Restricción n.12 (Reglamento de Seguridad Minera); Bases Técnicas Transversales, numeral 15.2 (certificaciones, sin código asignado — Consulta N.º 2)</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>Cap. 15, RT-17.06; Bases Técnicas Transversales RT-08.10 y Bases Administrativas Art. 14.2 (por verificar)</t>
+          <t>Cap. 15, RT-17.06; Bases Técnicas Transversales RT-08.10 (especificación del hardware de terreno); Bases Administrativas Art. 14.2</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -13870,7 +13870,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -14226,7 +14226,7 @@
         </is>
       </c>
       <c r="B2" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">

--- a/matriz trazabilidad/Matriz_Trazabilidad_Overfore_Informe1_v1.1.xlsx
+++ b/matriz trazabilidad/Matriz_Trazabilidad_Overfore_Informe1_v1.1.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Informe 1. Contiene los 228 requerimientos del catálogo v2.4 con su origen, su componente de arquitectura, su prueba de verificación y el criterio de aceptación que sostiene. La columna de paquete de la EDT se completa en el Informe 2, instancia en que el Formulario T-22 exige la estructura de descomposición del trabajo. Revisión de consistencia del 1 de septiembre de 2026: se alinean etapa, prioridad y origen con el catálogo v2.4.1, se corrigen los componentes de RF-CAR-005 y RF-CAR-008 y el criterio de RF-CAR-005, y se recalculan las hojas «Componentes» y «Cobertura de criterios».</t>
+          <t>Informe 1. Contiene los 228 requerimientos del catálogo v2.4 con su origen, su componente de arquitectura, su prueba de verificación y el criterio de aceptación que sostiene. La columna de paquete de la EDT se completa en el Informe 2, instancia en que el Formulario T-22 exige la estructura de descomposición del trabajo. Revisión de consistencia del 1 de septiembre de 2026: se alinean etapa, prioridad y origen con el catálogo v2.4.1, se corrigen los componentes de RF-CAR-005 y RF-CAR-008 y el criterio de RF-CAR-005, y se recalculan las hojas «Componentes» y «Cobertura de criterios». Revisión de consistencia del 4 de septiembre de 2026: la descripción de RF-AMB-014 y RF-AMB-015 se alinea literalmente con el catálogo, como exige la regla que ambos documentos declaran; RF-SSO-001 —registrar incidentes, cuasi accidentes, observaciones e inspecciones en el lugar del hecho— pasa a sostener también el criterio n.º 9, que hasta ahora no tenía trazado el requerimiento que lo habilita; y se recalcula la hoja «Cobertura de criterios».</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>n.º 13</t>
+          <t>n.º 9 · n.º 13</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Reconstruir hacia atrás la serie mensual de huella de carbono sobre los datos de actividad registrados desde la entrada en producción de la Etapa 1, aplicando a cada período los factores de emisión vigentes en ese período.</t>
+          <t>Reconstruir hacia atrás la serie mensual de huella de carbono sobre los datos de actividad registrados desde la entrada en producción de la Etapa 1, aplicando a cada período los factores de emisión vigentes en ese período y dejando registro del origen de cada dato utilizado.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Generar el expediente de evidencia auditable de la huella de carbono para el verificador tercero, con datos de actividad, factores de emisión versionados, memoria de cálculo por alcance y trazabilidad de cada cifra hasta su medición de origen.</t>
+          <t>Generar el expediente de evidencia auditable de la huella de carbono para el verificador tercero, incluyendo datos de actividad, factores de emisión versionados, memoria de cálculo por alcance y trazabilidad de cada cifra hasta su medición de origen, en formato abierto y documentado.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
